--- a/leakage/leakage_sensitivity_results.xlsx
+++ b/leakage/leakage_sensitivity_results.xlsx
@@ -575,10 +575,10 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C2">
-        <v>1.065383992100188E-88</v>
+        <v>7.624481727070574E-88</v>
       </c>
       <c r="D2">
         <v>2.92</v>
@@ -590,22 +590,22 @@
         <v>4.45</v>
       </c>
       <c r="G2">
-        <v>4.18</v>
+        <v>4.2</v>
       </c>
       <c r="H2">
-        <v>4.37</v>
+        <v>4.36</v>
       </c>
       <c r="I2">
         <v>5.55</v>
       </c>
       <c r="J2">
-        <v>5.35</v>
+        <v>5.37</v>
       </c>
       <c r="K2">
         <v>6.65</v>
       </c>
       <c r="L2">
-        <v>7.64</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -613,10 +613,10 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C3">
-        <v>3.745540189023439E-79</v>
+        <v>2.262482812444718E-78</v>
       </c>
       <c r="D3">
         <v>2.65</v>
@@ -628,22 +628,22 @@
         <v>4.38</v>
       </c>
       <c r="G3">
-        <v>4.45</v>
+        <v>4.47</v>
       </c>
       <c r="H3">
-        <v>4.7</v>
+        <v>4.69</v>
       </c>
       <c r="I3">
-        <v>5.39</v>
+        <v>5.38</v>
       </c>
       <c r="J3">
-        <v>5.44</v>
+        <v>5.46</v>
       </c>
       <c r="K3">
-        <v>6.62</v>
+        <v>6.61</v>
       </c>
       <c r="L3">
-        <v>7.58</v>
+        <v>7.57</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -651,10 +651,10 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C4">
-        <v>8.507059030763924E-79</v>
+        <v>5.2247198611943E-78</v>
       </c>
       <c r="D4">
         <v>2.65</v>
@@ -666,22 +666,22 @@
         <v>4.37</v>
       </c>
       <c r="G4">
-        <v>4.39</v>
+        <v>4.41</v>
       </c>
       <c r="H4">
-        <v>4.67</v>
+        <v>4.66</v>
       </c>
       <c r="I4">
-        <v>5.43</v>
+        <v>5.42</v>
       </c>
       <c r="J4">
-        <v>5.46</v>
+        <v>5.48</v>
       </c>
       <c r="K4">
-        <v>6.6</v>
+        <v>6.59</v>
       </c>
       <c r="L4">
-        <v>7.64</v>
+        <v>7.63</v>
       </c>
     </row>
   </sheetData>
@@ -728,10 +728,10 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E2">
         <v>8</v>
@@ -740,10 +740,10 @@
         <v>44</v>
       </c>
       <c r="G2">
-        <v>7.355097732893426E-13</v>
+        <v>9.961589912274726E-13</v>
       </c>
       <c r="H2">
-        <v>2.206529319868028E-12</v>
+        <v>2.988476973682418E-12</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -754,10 +754,10 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D3">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3">
         <v>8</v>
@@ -766,10 +766,10 @@
         <v>39</v>
       </c>
       <c r="G3">
-        <v>7.515902373986785E-16</v>
+        <v>1.146689141100141E-15</v>
       </c>
       <c r="H3">
-        <v>3.006360949594714E-15</v>
+        <v>4.586756564400565E-15</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -780,7 +780,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D4">
         <v>108</v>
@@ -789,13 +789,13 @@
         <v>1</v>
       </c>
       <c r="F4">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G4">
-        <v>0.001189194509431435</v>
+        <v>0.0008793658465944819</v>
       </c>
       <c r="H4">
-        <v>0.001189194509431435</v>
+        <v>0.0008793658465944819</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -806,10 +806,10 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D5">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -818,10 +818,10 @@
         <v>77</v>
       </c>
       <c r="G5">
-        <v>0.0001816842571225746</v>
+        <v>0.0002202055416705468</v>
       </c>
       <c r="H5">
-        <v>0.0003633685142451491</v>
+        <v>0.0004404110833410937</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -832,10 +832,10 @@
         <v>8</v>
       </c>
       <c r="C6">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D6">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -844,10 +844,10 @@
         <v>27</v>
       </c>
       <c r="G6">
-        <v>4.663557785402433E-23</v>
+        <v>7.433690956764144E-23</v>
       </c>
       <c r="H6">
-        <v>3.264490449781703E-22</v>
+        <v>4.460214574058486E-22</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -858,7 +858,7 @@
         <v>9</v>
       </c>
       <c r="C7">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D7">
         <v>150</v>
@@ -867,13 +867,13 @@
         <v>7</v>
       </c>
       <c r="F7">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G7">
-        <v>7.016352051097083E-23</v>
+        <v>5.985989799043596E-23</v>
       </c>
       <c r="H7">
-        <v>4.20981123065825E-22</v>
+        <v>4.190192859330517E-22</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -884,10 +884,10 @@
         <v>10</v>
       </c>
       <c r="C8">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D8">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -896,10 +896,10 @@
         <v>32</v>
       </c>
       <c r="G8">
-        <v>3.190845500235808E-20</v>
+        <v>5.00487551550948E-20</v>
       </c>
       <c r="H8">
-        <v>1.595422750117904E-19</v>
+        <v>2.50243775775474E-19</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -910,10 +910,10 @@
         <v>11</v>
       </c>
       <c r="C9">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D9">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -922,10 +922,10 @@
         <v>10</v>
       </c>
       <c r="G9">
-        <v>2.084180317698283E-30</v>
+        <v>3.08710812871881E-30</v>
       </c>
       <c r="H9">
-        <v>1.667344254158626E-29</v>
+        <v>2.469686502975048E-29</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -936,10 +936,10 @@
         <v>4</v>
       </c>
       <c r="C10">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D10">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E10">
         <v>6</v>
@@ -948,10 +948,10 @@
         <v>32</v>
       </c>
       <c r="G10">
-        <v>9.417303534992105E-15</v>
+        <v>1.289433134549984E-14</v>
       </c>
       <c r="H10">
-        <v>2.825191060497631E-14</v>
+        <v>3.868299403649953E-14</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -962,10 +962,10 @@
         <v>5</v>
       </c>
       <c r="C11">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D11">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E11">
         <v>5</v>
@@ -974,10 +974,10 @@
         <v>29</v>
       </c>
       <c r="G11">
-        <v>3.308921503768522E-17</v>
+        <v>5.116059916192754E-17</v>
       </c>
       <c r="H11">
-        <v>1.323568601507409E-16</v>
+        <v>2.046423966477102E-16</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -988,7 +988,7 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D12">
         <v>106</v>
@@ -997,13 +997,13 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G12">
-        <v>8.945436510546732E-05</v>
+        <v>6.117713538142455E-05</v>
       </c>
       <c r="H12">
-        <v>8.945436510546732E-05</v>
+        <v>6.117713538142455E-05</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1014,10 +1014,10 @@
         <v>7</v>
       </c>
       <c r="C13">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D13">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1026,10 +1026,10 @@
         <v>59</v>
       </c>
       <c r="G13">
-        <v>9.431304614944151E-06</v>
+        <v>1.145708119323906E-05</v>
       </c>
       <c r="H13">
-        <v>1.88626092298883E-05</v>
+        <v>2.291416238647812E-05</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1040,10 +1040,10 @@
         <v>8</v>
       </c>
       <c r="C14">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D14">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E14">
         <v>4</v>
@@ -1052,10 +1052,10 @@
         <v>24</v>
       </c>
       <c r="G14">
-        <v>1.000429687417045E-20</v>
+        <v>1.596534126710826E-20</v>
       </c>
       <c r="H14">
-        <v>6.002578124502272E-20</v>
+        <v>9.579204760264954E-20</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1066,7 +1066,7 @@
         <v>9</v>
       </c>
       <c r="C15">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D15">
         <v>143</v>
@@ -1075,13 +1075,13 @@
         <v>5</v>
       </c>
       <c r="F15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G15">
-        <v>2.992172467471127E-23</v>
+        <v>2.852969396161774E-23</v>
       </c>
       <c r="H15">
-        <v>2.094520727229789E-22</v>
+        <v>1.997078577313242E-22</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1092,10 +1092,10 @@
         <v>10</v>
       </c>
       <c r="C16">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D16">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -1104,10 +1104,10 @@
         <v>29</v>
       </c>
       <c r="G16">
-        <v>6.052769425165741E-18</v>
+        <v>9.471794782335629E-18</v>
       </c>
       <c r="H16">
-        <v>3.02638471258287E-17</v>
+        <v>4.735897391167815E-17</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1118,10 +1118,10 @@
         <v>11</v>
       </c>
       <c r="C17">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D17">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -1130,10 +1130,10 @@
         <v>9</v>
       </c>
       <c r="G17">
-        <v>2.800949438130745E-27</v>
+        <v>4.149055501176518E-27</v>
       </c>
       <c r="H17">
-        <v>2.240759550504596E-26</v>
+        <v>3.319244400941215E-26</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1144,10 +1144,10 @@
         <v>4</v>
       </c>
       <c r="C18">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D18">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E18">
         <v>4</v>
@@ -1156,10 +1156,10 @@
         <v>32</v>
       </c>
       <c r="G18">
-        <v>1.006647974183233E-14</v>
+        <v>1.375891068526028E-14</v>
       </c>
       <c r="H18">
-        <v>3.019943922549699E-14</v>
+        <v>4.127673205578084E-14</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1170,10 +1170,10 @@
         <v>5</v>
       </c>
       <c r="C19">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D19">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E19">
         <v>3</v>
@@ -1182,10 +1182,10 @@
         <v>29</v>
       </c>
       <c r="G19">
-        <v>4.413528605020745E-17</v>
+        <v>6.82315256182053E-17</v>
       </c>
       <c r="H19">
-        <v>1.765411442008298E-16</v>
+        <v>2.729261024728212E-16</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1196,7 +1196,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D20">
         <v>103</v>
@@ -1205,13 +1205,13 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G20">
-        <v>0.0002025593585656181</v>
+        <v>0.0001402898614432118</v>
       </c>
       <c r="H20">
-        <v>0.0002025593585656181</v>
+        <v>0.0001402898614432118</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1222,10 +1222,10 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D21">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1234,10 +1234,10 @@
         <v>59</v>
       </c>
       <c r="G21">
-        <v>9.733415800377336E-06</v>
+        <v>1.177100978781432E-05</v>
       </c>
       <c r="H21">
-        <v>1.946683160075467E-05</v>
+        <v>2.354201957562863E-05</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1248,10 +1248,10 @@
         <v>8</v>
       </c>
       <c r="C22">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D22">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E22">
         <v>2</v>
@@ -1260,10 +1260,10 @@
         <v>24</v>
       </c>
       <c r="G22">
-        <v>1.136578438313715E-20</v>
+        <v>1.812748073645652E-20</v>
       </c>
       <c r="H22">
-        <v>6.819470629882289E-20</v>
+        <v>1.087648844187391E-19</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1274,7 +1274,7 @@
         <v>9</v>
       </c>
       <c r="C23">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D23">
         <v>142</v>
@@ -1283,13 +1283,13 @@
         <v>3</v>
       </c>
       <c r="F23">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G23">
-        <v>3.640030522025346E-23</v>
+        <v>3.517094683735223E-23</v>
       </c>
       <c r="H23">
-        <v>2.548021365417742E-22</v>
+        <v>2.461966278614656E-22</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1300,10 +1300,10 @@
         <v>10</v>
       </c>
       <c r="C24">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D24">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E24">
         <v>2</v>
@@ -1312,10 +1312,10 @@
         <v>29</v>
       </c>
       <c r="G24">
-        <v>8.836984350356229E-18</v>
+        <v>1.380316950308123E-17</v>
       </c>
       <c r="H24">
-        <v>4.418492175178115E-17</v>
+        <v>6.901584751540613E-17</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1326,10 +1326,10 @@
         <v>11</v>
       </c>
       <c r="C25">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D25">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1338,10 +1338,10 @@
         <v>9</v>
       </c>
       <c r="G25">
-        <v>3.516908912916415E-27</v>
+        <v>5.205454183667516E-27</v>
       </c>
       <c r="H25">
-        <v>2.813527130333132E-26</v>
+        <v>4.164363346934013E-26</v>
       </c>
     </row>
   </sheetData>
@@ -1388,7 +1388,7 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D2">
         <v>2.76</v>
@@ -1397,7 +1397,7 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>6.303659180728687E-64</v>
+        <v>3.896296984712917E-63</v>
       </c>
       <c r="G2">
         <v>8</v>
@@ -1414,7 +1414,7 @@
         <v>13</v>
       </c>
       <c r="C3">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D3">
         <v>2.49</v>
@@ -1423,7 +1423,7 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>2.642912267427797E-60</v>
+        <v>1.314510974481539E-59</v>
       </c>
       <c r="G3">
         <v>8</v>
@@ -1440,16 +1440,16 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D4">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>6.865262223373803E-60</v>
+        <v>3.422332147988714E-59</v>
       </c>
       <c r="G4">
         <v>8</v>
@@ -1745,10 +1745,10 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -1757,13 +1757,13 @@
         <v>25</v>
       </c>
       <c r="H2">
-        <v>2.513487153772376E-10</v>
+        <v>3.651998062597235E-10</v>
       </c>
       <c r="I2">
-        <v>1.00539486150895E-09</v>
+        <v>1.460799225038894E-09</v>
       </c>
       <c r="J2">
-        <v>6.786415315185414E-09</v>
+        <v>9.495194962752812E-09</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1777,10 +1777,10 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E3">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -1789,13 +1789,13 @@
         <v>26</v>
       </c>
       <c r="H3">
-        <v>1.439194006593957E-09</v>
+        <v>2.272461459796527E-09</v>
       </c>
       <c r="I3">
-        <v>4.317582019781871E-09</v>
+        <v>6.817384379389582E-09</v>
       </c>
       <c r="J3">
-        <v>3.597985016484892E-08</v>
+        <v>5.681153649491318E-08</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1809,7 +1809,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E4">
         <v>69</v>
@@ -1818,16 +1818,16 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H4">
-        <v>0.001188719239899811</v>
+        <v>0.0008245932789587273</v>
       </c>
       <c r="I4">
-        <v>0.001188719239899811</v>
+        <v>0.0008245932789587273</v>
       </c>
       <c r="J4">
-        <v>0.0213969463181966</v>
+        <v>0.01566727230021582</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1841,10 +1841,10 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E5">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1853,13 +1853,13 @@
         <v>44</v>
       </c>
       <c r="H5">
-        <v>4.216271144371024E-05</v>
+        <v>5.253370892468792E-05</v>
       </c>
       <c r="I5">
-        <v>8.432542288742048E-05</v>
+        <v>0.0001050674178493758</v>
       </c>
       <c r="J5">
-        <v>0.0009275796517616252</v>
+        <v>0.001155741596343134</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1873,10 +1873,10 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E6">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -1885,13 +1885,13 @@
         <v>16</v>
       </c>
       <c r="H6">
-        <v>1.008522036552679E-14</v>
+        <v>1.61665487192987E-14</v>
       </c>
       <c r="I6">
-        <v>5.042610182763397E-14</v>
+        <v>8.083274359649349E-14</v>
       </c>
       <c r="J6">
-        <v>2.92471390600277E-13</v>
+        <v>4.688299128596623E-13</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1905,7 +1905,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E7">
         <v>97</v>
@@ -1914,16 +1914,16 @@
         <v>4</v>
       </c>
       <c r="G7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H7">
-        <v>2.830849364568079E-17</v>
+        <v>2.730652746881653E-17</v>
       </c>
       <c r="I7">
-        <v>1.981594555197655E-16</v>
+        <v>1.911456922817157E-16</v>
       </c>
       <c r="J7">
-        <v>8.775633030161046E-16</v>
+        <v>8.465023515333123E-16</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1937,10 +1937,10 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E8">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1949,13 +1949,13 @@
         <v>16</v>
       </c>
       <c r="H8">
-        <v>2.793230769851903E-15</v>
+        <v>4.158341692819542E-15</v>
       </c>
       <c r="I8">
-        <v>1.675938461911142E-14</v>
+        <v>2.495005015691725E-14</v>
       </c>
       <c r="J8">
-        <v>8.379692309555709E-14</v>
+        <v>1.247502507845863E-13</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1969,10 +1969,10 @@
         <v>11</v>
       </c>
       <c r="D9">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E9">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1981,13 +1981,13 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>1.269808458939636E-19</v>
+        <v>1.880510352352555E-19</v>
       </c>
       <c r="I9">
-        <v>1.015846767151709E-18</v>
+        <v>1.504408281882044E-18</v>
       </c>
       <c r="J9">
-        <v>4.063387068606835E-18</v>
+        <v>6.017633127528176E-18</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -2001,10 +2001,10 @@
         <v>4</v>
       </c>
       <c r="D10">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E10">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F10">
         <v>4</v>
@@ -2013,13 +2013,13 @@
         <v>19</v>
       </c>
       <c r="H10">
-        <v>5.87973149018149E-11</v>
+        <v>8.61672292533618E-11</v>
       </c>
       <c r="I10">
-        <v>2.351892596072596E-10</v>
+        <v>3.446689170134472E-10</v>
       </c>
       <c r="J10">
-        <v>1.646324817250817E-09</v>
+        <v>2.412682419094131E-09</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -2033,10 +2033,10 @@
         <v>5</v>
       </c>
       <c r="D11">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E11">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F11">
         <v>3</v>
@@ -2045,13 +2045,13 @@
         <v>20</v>
       </c>
       <c r="H11">
-        <v>3.094367017172172E-09</v>
+        <v>4.850620153309543E-09</v>
       </c>
       <c r="I11">
-        <v>9.283101051516516E-09</v>
+        <v>1.455186045992863E-08</v>
       </c>
       <c r="J11">
-        <v>7.73591754293043E-08</v>
+        <v>1.212655038327386E-07</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -2065,7 +2065,7 @@
         <v>6</v>
       </c>
       <c r="D12">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E12">
         <v>68</v>
@@ -2074,16 +2074,16 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H12">
-        <v>0.0002723313035226144</v>
+        <v>0.0001803685873609318</v>
       </c>
       <c r="I12">
-        <v>0.0002723313035226144</v>
+        <v>0.0001803685873609318</v>
       </c>
       <c r="J12">
-        <v>0.005446626070452289</v>
+        <v>0.003607371747218636</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -2097,10 +2097,10 @@
         <v>7</v>
       </c>
       <c r="D13">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E13">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -2109,13 +2109,13 @@
         <v>34</v>
       </c>
       <c r="H13">
-        <v>1.059137467873273E-05</v>
+        <v>1.271384505073672E-05</v>
       </c>
       <c r="I13">
-        <v>2.118274935746545E-05</v>
+        <v>2.542769010147344E-05</v>
       </c>
       <c r="J13">
-        <v>0.00023301024293212</v>
+        <v>0.0002728026951067758</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -2129,10 +2129,10 @@
         <v>8</v>
       </c>
       <c r="D14">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E14">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F14">
         <v>2</v>
@@ -2141,13 +2141,13 @@
         <v>14</v>
       </c>
       <c r="H14">
-        <v>1.866572438527255E-13</v>
+        <v>2.993004053174279E-13</v>
       </c>
       <c r="I14">
-        <v>9.332862192636273E-13</v>
+        <v>1.49650202658714E-12</v>
       </c>
       <c r="J14">
-        <v>5.413060071729038E-12</v>
+        <v>8.67971175420541E-12</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -2161,7 +2161,7 @@
         <v>9</v>
       </c>
       <c r="D15">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E15">
         <v>93</v>
@@ -2170,16 +2170,16 @@
         <v>3</v>
       </c>
       <c r="G15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H15">
-        <v>9.262548164540418E-17</v>
+        <v>1.033816623948277E-16</v>
       </c>
       <c r="I15">
-        <v>6.483783715178292E-16</v>
+        <v>7.236716367637937E-16</v>
       </c>
       <c r="J15">
-        <v>2.87138993100753E-15</v>
+        <v>3.204831534239658E-15</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -2193,10 +2193,10 @@
         <v>10</v>
       </c>
       <c r="D16">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E16">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -2205,13 +2205,13 @@
         <v>13</v>
       </c>
       <c r="H16">
-        <v>4.728963421467444E-14</v>
+        <v>6.957129565878172E-14</v>
       </c>
       <c r="I16">
-        <v>2.837378052880466E-13</v>
+        <v>4.174277739526903E-13</v>
       </c>
       <c r="J16">
-        <v>1.418689026440233E-12</v>
+        <v>2.087138869763452E-12</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2225,10 +2225,10 @@
         <v>11</v>
       </c>
       <c r="D17">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E17">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -2237,13 +2237,13 @@
         <v>5</v>
       </c>
       <c r="H17">
-        <v>8.745584799810588E-18</v>
+        <v>1.293809293778917E-17</v>
       </c>
       <c r="I17">
-        <v>6.99646783984847E-17</v>
+        <v>1.035047435023133E-16</v>
       </c>
       <c r="J17">
-        <v>2.798587135939388E-16</v>
+        <v>4.140189740092534E-16</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2257,10 +2257,10 @@
         <v>4</v>
       </c>
       <c r="D18">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E18">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F18">
         <v>3</v>
@@ -2269,13 +2269,13 @@
         <v>19</v>
       </c>
       <c r="H18">
-        <v>6.160292851982033E-11</v>
+        <v>9.006400499566604E-11</v>
       </c>
       <c r="I18">
-        <v>2.464117140792813E-10</v>
+        <v>3.602560199826642E-10</v>
       </c>
       <c r="J18">
-        <v>1.724881998554969E-09</v>
+        <v>2.521792139878649E-09</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2289,10 +2289,10 @@
         <v>5</v>
       </c>
       <c r="D19">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E19">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F19">
         <v>2</v>
@@ -2301,13 +2301,13 @@
         <v>20</v>
       </c>
       <c r="H19">
-        <v>4.359652937871193E-09</v>
+        <v>6.833911429226732E-09</v>
       </c>
       <c r="I19">
-        <v>1.307895881361358E-08</v>
+        <v>2.05017342876802E-08</v>
       </c>
       <c r="J19">
-        <v>1.089913234467798E-07</v>
+        <v>1.708477857306683E-07</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -2321,7 +2321,7 @@
         <v>6</v>
       </c>
       <c r="D20">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E20">
         <v>66</v>
@@ -2330,16 +2330,16 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H20">
-        <v>0.0004246263470098391</v>
+        <v>0.0002835265025860588</v>
       </c>
       <c r="I20">
-        <v>0.0004246263470098391</v>
+        <v>0.0002835265025860588</v>
       </c>
       <c r="J20">
-        <v>0.008492526940196782</v>
+        <v>0.005670530051721176</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -2353,10 +2353,10 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E21">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -2365,13 +2365,13 @@
         <v>34</v>
       </c>
       <c r="H21">
-        <v>1.09444011804217E-05</v>
+        <v>1.304342825290132E-05</v>
       </c>
       <c r="I21">
-        <v>2.188880236084341E-05</v>
+        <v>2.608685650580264E-05</v>
       </c>
       <c r="J21">
-        <v>0.0002407768259692775</v>
+        <v>0.0002739119933109278</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -2385,10 +2385,10 @@
         <v>8</v>
       </c>
       <c r="D22">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E22">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -2397,13 +2397,13 @@
         <v>14</v>
       </c>
       <c r="H22">
-        <v>2.079623324611684E-13</v>
+        <v>3.331165845546256E-13</v>
       </c>
       <c r="I22">
-        <v>1.039811662305842E-12</v>
+        <v>1.665582922773128E-12</v>
       </c>
       <c r="J22">
-        <v>6.030907641373883E-12</v>
+        <v>9.660380952084142E-12</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -2417,7 +2417,7 @@
         <v>9</v>
       </c>
       <c r="D23">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E23">
         <v>92</v>
@@ -2426,16 +2426,16 @@
         <v>2</v>
       </c>
       <c r="G23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H23">
-        <v>1.164717148189017E-16</v>
+        <v>1.333450337905004E-16</v>
       </c>
       <c r="I23">
-        <v>8.15302003732312E-16</v>
+        <v>9.334152365335028E-16</v>
       </c>
       <c r="J23">
-        <v>3.610623159385953E-15</v>
+        <v>4.133696047505512E-15</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -2449,10 +2449,10 @@
         <v>10</v>
       </c>
       <c r="D24">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E24">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -2461,13 +2461,13 @@
         <v>13</v>
       </c>
       <c r="H24">
-        <v>6.878573737329029E-14</v>
+        <v>1.008792884274257E-13</v>
       </c>
       <c r="I24">
-        <v>4.127144242397417E-13</v>
+        <v>6.052757305645545E-13</v>
       </c>
       <c r="J24">
-        <v>2.063572121198709E-12</v>
+        <v>3.026378652822772E-12</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -2481,10 +2481,10 @@
         <v>11</v>
       </c>
       <c r="D25">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E25">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -2493,13 +2493,13 @@
         <v>5</v>
       </c>
       <c r="H25">
-        <v>1.114710784203997E-17</v>
+        <v>1.647125094700997E-17</v>
       </c>
       <c r="I25">
-        <v>8.917686273631976E-17</v>
+        <v>1.317700075760797E-16</v>
       </c>
       <c r="J25">
-        <v>3.567074509452791E-16</v>
+        <v>5.270800303043189E-16</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -2659,7 +2659,7 @@
         <v>1.873509493311524E-09</v>
       </c>
       <c r="J30">
-        <v>6.958749546585661E-09</v>
+        <v>7.226393759915878E-09</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -2947,7 +2947,7 @@
         <v>4.960049001941378E-05</v>
       </c>
       <c r="J39">
-        <v>0.0002604025726019224</v>
+        <v>0.0002728026951067758</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -3203,7 +3203,7 @@
         <v>4.960049001941378E-05</v>
       </c>
       <c r="J47">
-        <v>0.0002604025726019224</v>
+        <v>0.0002728026951067758</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -4227,7 +4227,7 @@
         <v>0.007896779511033847</v>
       </c>
       <c r="J79">
-        <v>0.01875485133870539</v>
+        <v>0.01776775389982616</v>
       </c>
     </row>
     <row r="80" spans="1:10">
